--- a/0-complete_literature_data/data_temp.xlsx
+++ b/0-complete_literature_data/data_temp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yibinjiang\Documents\GitHub\np_at_mof\2-complete_literature_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yibinjiang\Documents\GitHub\NP-MOF\0-complete_literature_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D36794-CCD0-4CDE-AAF0-FCA5FC162C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51A250E-7A88-482C-9EAA-D657D69971E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="215">
   <si>
     <r>
       <rPr>
@@ -828,8 +828,187 @@
     <t>UiO-68-NH2</t>
   </si>
   <si>
-    <r>
-      <t>SI-70℃</t>
+    <t>Zn(pip)(dpb)(Zn,MOF-3)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT02ce3bbb.I"/>
+        <charset val="134"/>
+      </rPr>
+      <t>pip=5-(prop-2-yn-1-yloxy)isophthalic acid;dpb=1,4-di(pyridin-4-yl)benzene</t>
+    </r>
+  </si>
+  <si>
+    <t>[Zn(pip)(bpy)](Zn，MOF-1)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>H2pip=5-(prop-2-yn-1-yloxy)isophthalic acid;bpy=4,4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT8608a8d1+20"/>
+        <charset val="134"/>
+      </rPr>
+      <t>′</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-bipyridine</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[Cd(pip) (bpe)](</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Cd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MOF-2)</t>
+    </r>
+  </si>
+  <si>
+    <t>H2pip=5-(prop-2-yn-1-yloxy)isophthalic acid;bpe=1,2-di(pyridin-4-yl)ethane</t>
+  </si>
+  <si>
+    <t>[Zn(bip)(dpb)](Zn,MOF-A)</t>
+  </si>
+  <si>
+    <t>bip = 5-(benzyloxy)-isophthalate;dpb=1,4-di(pyridin-4-yl)benzene</t>
+  </si>
+  <si>
+    <t>PCN-224(Zr)</t>
+  </si>
+  <si>
+    <t>ZIF-67(Zn)</t>
+  </si>
+  <si>
+    <t>HKUST-1-R(Cu)</t>
+  </si>
+  <si>
+    <t>134-1</t>
+  </si>
+  <si>
+    <t>UiO-66-2OH</t>
+  </si>
+  <si>
+    <t>MIL-101-Fx</t>
+  </si>
+  <si>
+    <t>x=3, 5, 7, 11, 15</t>
+  </si>
+  <si>
+    <t>DUT-67(Zr)</t>
+  </si>
+  <si>
+    <t>UiO-67</t>
+  </si>
+  <si>
+    <t>PCN-222(Zr)</t>
+  </si>
+  <si>
+    <t>arc plasma deposition (APD)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NHC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="STIXGeneral-Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="STIX2Text-Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">MIL-101(Cr) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SI+</t>
     </r>
     <r>
       <rPr>
@@ -838,13 +1017,8 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>加热</t>
-    </r>
-  </si>
-  <si>
-    <t>Zn(pip)(dpb)(Zn,MOF-3)</t>
-  </si>
-  <si>
+      <t>在持续搅拌条件下于</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -852,29 +1026,34 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
+      <t>383 K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT02ce3bbb.I"/>
+      <t>缓慢蒸发乙酰丙酮溶剂</t>
+    </r>
+  </si>
+  <si>
+    <t>MIL-101-NH2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>pip=5-(prop-2-yn-1-yloxy)isophthalic acid;dpb=1,4-di(pyridin-4-yl)benzene</t>
-    </r>
-  </si>
-  <si>
-    <t>[Zn(pip)(bpy)](Zn，MOF-1)</t>
+      <t>反应后粒径保持很小</t>
+    </r>
+  </si>
+  <si>
+    <t>Ir</t>
   </si>
   <si>
     <r>
@@ -884,26 +1063,180 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>H2pip=5-(prop-2-yn-1-yloxy)isophthalic acid;bpy=4,4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT8608a8d1+20"/>
-        <charset val="134"/>
-      </rPr>
-      <t>′</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>ZIF-8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>(Zn)</t>
+    </r>
+  </si>
+  <si>
+    <t>118-1</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>Zr6(μ3-O)4(μ3-OH)4(bpdc)5.94(L1)0.06 (UiO-67-1)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="AdvOT2e364b11"/>
         <charset val="134"/>
       </rPr>
-      <t>-bipyridine</t>
-    </r>
+      <t>The [Ir(ppy)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(bpy)]Cl-derived dicarboxylic acids H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT51c1769e"/>
+        <charset val="134"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT51c1769e"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> was synthesized by treating [Ir(ppy)2Cl]2 with diethyl (2,2′-bipyridine)-5,5′-dicarboxylate (Et2L1) </t>
+    </r>
+  </si>
+  <si>
+    <t>汪老师的文章，从TEM图判断为0</t>
+  </si>
+  <si>
+    <t>Zr6(μ3-O)4(μ3-OH)4(L2)6·64DMF (UiO-67-2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The [Ir(ppy)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="AdvOT2e364b11"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(bpy)]Cl-derived dicarboxylic acids  H2L2 was synthesized by treating [Ir(ppy)2Cl]2 with dimethyl (2,2′-bipyridine)-5,5′-dibenzoate (Me2L2)</t>
+    </r>
+  </si>
+  <si>
+    <t>UiO-66-NH2(Zr)</t>
+  </si>
+  <si>
+    <t>DUT-5(Al)</t>
+  </si>
+  <si>
+    <t>89-1</t>
+  </si>
+  <si>
+    <t>MOF-525(Zr)</t>
+  </si>
+  <si>
+    <t>MOF-74(Co)</t>
+  </si>
+  <si>
+    <t>PCN-777(Zr)</t>
+  </si>
+  <si>
+    <t>UiO-68</t>
+  </si>
+  <si>
+    <t>NU-901(Zr)</t>
+  </si>
+  <si>
+    <t>Fe-MOf</t>
+  </si>
+  <si>
+    <t>MOF-801</t>
+  </si>
+  <si>
+    <t>UiO-66-NH-SH</t>
+  </si>
+  <si>
+    <t>UiO-66-F</t>
+  </si>
+  <si>
+    <t>UiO-66-OH</t>
+  </si>
+  <si>
+    <t>PCN-224</t>
+  </si>
+  <si>
+    <t>no catalytic reaction</t>
+  </si>
+  <si>
+    <t>MIL-101</t>
+  </si>
+  <si>
+    <t>Rh</t>
+  </si>
+  <si>
+    <t>Cu</t>
   </si>
   <si>
     <r>
@@ -913,77 +1246,29 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>[Cd(pip) (bpe)](</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+      <t>NU-1000-NH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5.5"/>
         <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="AdvOT9b12cd41"/>
         <charset val="134"/>
       </rPr>
-      <t>Cd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <color rgb="FF000000"/>
-        <rFont val="宋体"/>
+        <rFont val="AdvOT9b12cd41"/>
         <charset val="134"/>
       </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MOF-2)</t>
-    </r>
-  </si>
-  <si>
-    <t>H2pip=5-(prop-2-yn-1-yloxy)isophthalic acid;bpe=1,2-di(pyridin-4-yl)ethane</t>
-  </si>
-  <si>
-    <t>[Zn(bip)(dpb)](Zn,MOF-A)</t>
-  </si>
-  <si>
-    <t>bip = 5-(benzyloxy)-isophthalate;dpb=1,4-di(pyridin-4-yl)benzene</t>
-  </si>
-  <si>
-    <t>PCN-224(Zr)</t>
-  </si>
-  <si>
-    <t>ZIF-67(Zn)</t>
-  </si>
-  <si>
-    <t>HKUST-1-R(Cu)</t>
-  </si>
-  <si>
-    <t>134-1</t>
-  </si>
-  <si>
-    <t>UiO-66-2OH</t>
-  </si>
-  <si>
-    <t>MIL-101-Fx</t>
-  </si>
-  <si>
-    <t>x=3, 5, 7, 11, 15</t>
-  </si>
-  <si>
-    <t>DUT-67(Zr)</t>
-  </si>
-  <si>
-    <t>UiO-67</t>
-  </si>
-  <si>
-    <t>PCN-222(Zr)</t>
-  </si>
-  <si>
-    <t>arc plasma deposition (APD)</t>
+      <t>/PrSH(Zr)</t>
+    </r>
+  </si>
+  <si>
+    <t>2Bn@UiO-67</t>
   </si>
   <si>
     <r>
@@ -993,30 +1278,39 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>NHC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
+      <t>NU-1000-NH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5.5"/>
         <color rgb="FF000000"/>
-        <rFont val="STIXGeneral-Regular"/>
+        <rFont val="AdvOT9b12cd41"/>
         <charset val="134"/>
       </rPr>
-      <t>−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="STIX2Text-Regular"/>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>Co</t>
+  </si>
+  <si>
+    <t>incipient wetness impregnation</t>
+  </si>
+  <si>
+    <t>118-2</t>
+  </si>
+  <si>
+    <t>Ni</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">MIL-101(Cr) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SI-100℃</t>
+      <t>C384H192N48O96Tb16(MesMOF-1(Tb)</t>
     </r>
     <r>
       <rPr>
@@ -1025,8 +1319,115 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>加热</t>
-    </r>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>MIL-120(Al)</t>
+  </si>
+  <si>
+    <t>MOF-545(Zr)</t>
+  </si>
+  <si>
+    <t>Ru</t>
+  </si>
+  <si>
+    <t>After Reaction</t>
+  </si>
+  <si>
+    <t>La(1,3,5-BTC)·6(H2O)</t>
+  </si>
+  <si>
+    <t>HKUST-1(Cu)</t>
+  </si>
+  <si>
+    <t>AgAu</t>
+  </si>
+  <si>
+    <t>AgPd</t>
+  </si>
+  <si>
+    <t>PdAg</t>
+  </si>
+  <si>
+    <t>PtAg</t>
+  </si>
+  <si>
+    <t>AuAg</t>
+  </si>
+  <si>
+    <t>AuPd</t>
+  </si>
+  <si>
+    <t>ED-MIL-101</t>
+  </si>
+  <si>
+    <t>AuNi</t>
+  </si>
+  <si>
+    <t>AuPt</t>
+  </si>
+  <si>
+    <t>Bottle-around-ship+SI</t>
+  </si>
+  <si>
+    <t>AuPdCu</t>
+  </si>
+  <si>
+    <t>AuCo</t>
+  </si>
+  <si>
+    <t>PtAu</t>
+  </si>
+  <si>
+    <t>PdAu</t>
+  </si>
+  <si>
+    <t>AuCu</t>
+  </si>
+  <si>
+    <t>Bottle-around-ship+Mechanical Mixing</t>
+  </si>
+  <si>
+    <t>PtAuPd</t>
+  </si>
+  <si>
+    <t>PdCu</t>
+  </si>
+  <si>
+    <t>NiPd</t>
+  </si>
+  <si>
+    <t>PdCo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgPd
+</t>
+  </si>
+  <si>
+    <t>MIL-125-NH2-DPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgPd, DPA=polydopamine
+</t>
+  </si>
+  <si>
+    <t>PdNi</t>
+  </si>
+  <si>
+    <t>PdPt</t>
+  </si>
+  <si>
+    <t>CuPd</t>
+  </si>
+  <si>
+    <t>NiPt</t>
+  </si>
+  <si>
+    <t>PtCo</t>
+  </si>
+  <si>
+    <t>RuPt</t>
   </si>
   <si>
     <r>
@@ -1036,7 +1437,72 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>SI+</t>
+      <t>Cu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6.3"/>
+        <color rgb="FF231F20"/>
+        <rFont val="ScalaPro-Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <rFont val="ScalaPro-Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(HHTP)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6.3"/>
+        <color rgb="FF231F20"/>
+        <rFont val="ScalaPro-Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>RhRu</t>
+  </si>
+  <si>
+    <t>CuNi</t>
+  </si>
+  <si>
+    <t>SI+ high-intensity ultrasound irradiation</t>
+  </si>
+  <si>
+    <t>CuCoNi</t>
+  </si>
+  <si>
+    <t>CuCo</t>
+  </si>
+  <si>
+    <t>UiO-67-Pd(II)-L-Pro</t>
+  </si>
+  <si>
+    <t>NiRu</t>
+  </si>
+  <si>
+    <t>PtCu</t>
+  </si>
+  <si>
+    <t>γ-radiation</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SI-70℃</t>
     </r>
     <r>
       <rPr>
@@ -1045,8 +1511,10 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>在持续搅拌条件下于</t>
-    </r>
+      <t>加热</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1054,7 +1522,7 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>383 K</t>
+      <t>SI-100℃</t>
     </r>
     <r>
       <rPr>
@@ -1063,13 +1531,19 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>缓慢蒸发乙酰丙酮溶剂</t>
-    </r>
-  </si>
-  <si>
-    <t>MIL-101-NH2</t>
-  </si>
-  <si>
+      <t>加热</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SI-5 MPa CO2-200℃</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1077,468 +1551,52 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>反应后粒径保持很小</t>
-    </r>
-  </si>
-  <si>
-    <t>Ir</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>烧釜</t>
+    </r>
+  </si>
+  <si>
+    <t>UiO-bpydc1/bpdc5</t>
+  </si>
+  <si>
+    <r>
+      <t>Cu</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>ZIF-8</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>(Zn)</t>
-    </r>
-  </si>
-  <si>
-    <t>118-1</t>
-  </si>
-  <si>
-    <t>Pt</t>
-  </si>
-  <si>
-    <t>Zr6(μ3-O)4(μ3-OH)4(bpdc)5.94(L1)0.06 (UiO-67-1)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t>The [Ir(ppy)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(bpy)]Cl-derived dicarboxylic acids H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT51c1769e"/>
-        <charset val="134"/>
-      </rPr>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT51c1769e"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> was synthesized by treating [Ir(ppy)2Cl]2 with diethyl (2,2′-bipyridine)-5,5′-dicarboxylate (Et2L1) </t>
-    </r>
-  </si>
-  <si>
-    <t>汪老师的文章，从TEM图判断为0</t>
-  </si>
-  <si>
-    <t>Zr6(μ3-O)4(μ3-OH)4(L2)6·64DMF (UiO-67-2)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t>The [Ir(ppy)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT2e364b11"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(bpy)]Cl-derived dicarboxylic acids  H2L2 was synthesized by treating [Ir(ppy)2Cl]2 with dimethyl (2,2′-bipyridine)-5,5′-dibenzoate (Me2L2)</t>
-    </r>
-  </si>
-  <si>
-    <t>UiO-66-NH2(Zr)</t>
-  </si>
-  <si>
-    <t>DUT-5(Al)</t>
-  </si>
-  <si>
-    <t>89-1</t>
-  </si>
-  <si>
-    <t>MOF-525(Zr)</t>
-  </si>
-  <si>
-    <t>MOF-74(Co)</t>
-  </si>
-  <si>
-    <t>PCN-777(Zr)</t>
-  </si>
-  <si>
-    <t>UiO-68</t>
-  </si>
-  <si>
-    <t>NU-901(Zr)</t>
-  </si>
-  <si>
-    <t>Fe-MOf</t>
-  </si>
-  <si>
-    <t>MOF-801</t>
-  </si>
-  <si>
-    <t>UiO-66-NH-SH</t>
-  </si>
-  <si>
-    <t>UiO-66-F</t>
-  </si>
-  <si>
-    <t>UiO-66-OH</t>
-  </si>
-  <si>
-    <t>PCN-224</t>
-  </si>
-  <si>
-    <t>no catalytic reaction</t>
-  </si>
-  <si>
-    <t>MIL-101</t>
-  </si>
-  <si>
-    <t>Rh</t>
-  </si>
-  <si>
-    <t>Cu</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>NU-1000-NH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT9b12cd41"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT9b12cd41"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/PrSH(Zr)</t>
-    </r>
-  </si>
-  <si>
-    <t>2Bn@UiO-67</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>(HHTP)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>NU-1000-NH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="5.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="AdvOT9b12cd41"/>
-        <charset val="134"/>
-      </rPr>
       <t>2</t>
     </r>
-  </si>
-  <si>
-    <t>Co</t>
-  </si>
-  <si>
-    <t>incipient wetness impregnation</t>
-  </si>
-  <si>
-    <t>118-2</t>
-  </si>
-  <si>
-    <t>Ni</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>C384H192N48O96Tb16(MesMOF-1(Tb)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <t>MIL-120(Al)</t>
-  </si>
-  <si>
-    <t>MOF-545(Zr)</t>
-  </si>
-  <si>
-    <t>Ru</t>
-  </si>
-  <si>
-    <t>After Reaction</t>
-  </si>
-  <si>
-    <t>La(1,3,5-BTC)·6(H2O)</t>
-  </si>
-  <si>
-    <r>
-      <t>SI-5 MPa CO2-200℃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>烧釜</t>
-    </r>
-  </si>
-  <si>
-    <t>HKUST-1(Cu)</t>
-  </si>
-  <si>
-    <t>AgAu</t>
-  </si>
-  <si>
-    <t>AgPd</t>
-  </si>
-  <si>
-    <t>PdAg</t>
-  </si>
-  <si>
-    <t>PtAg</t>
-  </si>
-  <si>
-    <t>AuAg</t>
-  </si>
-  <si>
-    <t>AuPd</t>
-  </si>
-  <si>
-    <t>ED-MIL-101</t>
-  </si>
-  <si>
-    <t>AuNi</t>
-  </si>
-  <si>
-    <t>AuPt</t>
-  </si>
-  <si>
-    <t>Bottle-around-ship+SI</t>
-  </si>
-  <si>
-    <t>AuPdCu</t>
-  </si>
-  <si>
-    <t>AuCo</t>
-  </si>
-  <si>
-    <t>PtAu</t>
-  </si>
-  <si>
-    <t>PdAu</t>
-  </si>
-  <si>
-    <t>AuCu</t>
-  </si>
-  <si>
-    <t>Bottle-around-ship+Mechanical Mixing</t>
-  </si>
-  <si>
-    <t>PtAuPd</t>
-  </si>
-  <si>
-    <t>PdCu</t>
-  </si>
-  <si>
-    <t>NiPd</t>
-  </si>
-  <si>
-    <t>PdCo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AgPd
-</t>
-  </si>
-  <si>
-    <t>MIL-125-NH2-DPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AgPd, DPA=polydopamine
-</t>
-  </si>
-  <si>
-    <t>PdNi</t>
-  </si>
-  <si>
-    <t>PdPt</t>
-  </si>
-  <si>
-    <t>CuPd</t>
-  </si>
-  <si>
-    <t>NiPt</t>
-  </si>
-  <si>
-    <t>PtCo</t>
-  </si>
-  <si>
-    <t>RuPt</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Cu</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6.3"/>
-        <color rgb="FF231F20"/>
-        <rFont val="ScalaPro-Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-        <rFont val="ScalaPro-Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(HHTP)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6.3"/>
-        <color rgb="FF231F20"/>
-        <rFont val="ScalaPro-Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>RhRu</t>
-  </si>
-  <si>
-    <t>CuNi</t>
-  </si>
-  <si>
-    <t>SI+ high-intensity ultrasound irradiation</t>
-  </si>
-  <si>
-    <t>CuCoNi</t>
-  </si>
-  <si>
-    <t>CuCo</t>
-  </si>
-  <si>
-    <t>UiO-67-Pd(II)-L-Pro</t>
-  </si>
-  <si>
-    <t>NiRu</t>
-  </si>
-  <si>
-    <t>PtCu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1758,8 +1816,33 @@
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF231F20"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6.45"/>
+      <color rgb="FF000000"/>
+      <name val="AdvGulliv-R"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1826,6 +1909,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1839,7 +1928,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1924,6 +2013,24 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2205,7 +2312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N352"/>
+  <dimension ref="A1:N356"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -2959,26 +3066,24 @@
       <c r="K33" s="1"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="7" t="s">
-        <v>46</v>
+      <c r="A34" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="B34" s="1">
         <v>33</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G34" s="1">
-        <v>4</v>
+      <c r="C34" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="30">
+        <v>1</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30">
+        <v>244</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
@@ -2992,17 +3097,19 @@
         <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F35" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="G35" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
@@ -3016,7 +3123,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -3046,7 +3153,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1">
@@ -3056,7 +3163,7 @@
       <c r="I37" s="8"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:11" ht="15.75">
+    <row r="38" spans="1:11">
       <c r="A38" s="7" t="s">
         <v>46</v>
       </c>
@@ -3064,25 +3171,23 @@
         <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>52</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="K38" s="1"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" ht="15.75">
       <c r="A39" s="7" t="s">
         <v>46</v>
       </c>
@@ -3090,17 +3195,19 @@
         <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F39" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>52</v>
+      </c>
       <c r="G39" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -3114,7 +3221,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -3138,7 +3245,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -3162,7 +3269,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D42" s="1">
         <v>1</v>
@@ -3172,7 +3279,7 @@
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
@@ -3186,23 +3293,23 @@
         <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1">
-        <v>21</v>
-      </c>
-      <c r="H43" s="10"/>
+        <v>18</v>
+      </c>
+      <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" ht="15.75">
+    <row r="44" spans="1:11">
       <c r="A44" s="7" t="s">
         <v>46</v>
       </c>
@@ -3215,14 +3322,14 @@
       <c r="D44" s="1">
         <v>1</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>32</v>
+      <c r="E44" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1">
         <v>21</v>
       </c>
-      <c r="H44" s="11"/>
+      <c r="H44" s="10"/>
       <c r="I44" s="8"/>
       <c r="K44" s="1"/>
     </row>
@@ -3239,12 +3346,10 @@
       <c r="D45" s="1">
         <v>1</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>56</v>
-      </c>
+      <c r="E45" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" s="1"/>
       <c r="G45" s="1">
         <v>21</v>
       </c>
@@ -3252,7 +3357,7 @@
       <c r="I45" s="8"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" ht="15.75">
       <c r="A46" s="7" t="s">
         <v>46</v>
       </c>
@@ -3260,17 +3365,19 @@
         <v>45</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F46" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>56</v>
+      </c>
       <c r="G46" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H46" s="11"/>
       <c r="I46" s="8"/>
@@ -3284,7 +3391,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -3296,7 +3403,7 @@
       <c r="G47" s="1">
         <v>23</v>
       </c>
-      <c r="H47" s="12"/>
+      <c r="H47" s="11"/>
       <c r="I47" s="8"/>
       <c r="K47" s="1"/>
     </row>
@@ -3308,21 +3415,19 @@
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D48" s="4">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>59</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F48" s="1"/>
       <c r="G48" s="1">
-        <v>29</v>
-      </c>
-      <c r="H48" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="H48" s="12"/>
       <c r="I48" s="8"/>
       <c r="K48" s="1"/>
     </row>
@@ -3334,17 +3439,19 @@
         <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="D49" s="4">
+        <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="G49" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
@@ -3358,17 +3465,17 @@
         <v>49</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
@@ -3382,17 +3489,17 @@
         <v>50</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D51" s="1">
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
@@ -3406,7 +3513,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" s="1">
         <v>1</v>
@@ -3416,21 +3523,21 @@
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
       <c r="K52" s="1"/>
     </row>
-    <row r="53" spans="1:11" ht="15.75">
+    <row r="53" spans="1:11">
       <c r="A53" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B53" s="1">
         <v>52</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>62</v>
+      <c r="C53" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -3438,9 +3545,7 @@
       <c r="E53" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>63</v>
-      </c>
+      <c r="F53" s="1"/>
       <c r="G53" s="1">
         <v>58</v>
       </c>
@@ -3448,15 +3553,15 @@
       <c r="I53" s="8"/>
       <c r="K53" s="1"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" ht="15.75">
       <c r="A54" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B54" s="1">
         <v>53</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>64</v>
+      <c r="C54" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
@@ -3464,9 +3569,11 @@
       <c r="E54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F54" s="1"/>
+      <c r="F54" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="G54" s="1">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
@@ -3480,7 +3587,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
@@ -3490,10 +3597,11 @@
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
+      <c r="K55" s="1"/>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="7" t="s">
@@ -3503,7 +3611,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -3513,7 +3621,7 @@
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -3526,7 +3634,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
@@ -3549,7 +3657,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
@@ -3559,7 +3667,7 @@
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -3572,17 +3680,17 @@
         <v>58</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -3595,17 +3703,17 @@
         <v>59</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -3618,7 +3726,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D61" s="1">
         <v>1</v>
@@ -3641,7 +3749,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -3651,7 +3759,7 @@
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -3664,7 +3772,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
@@ -3674,7 +3782,7 @@
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -3687,7 +3795,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -3697,7 +3805,7 @@
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -3710,7 +3818,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -3718,24 +3826,22 @@
       <c r="E65" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="F65" s="1"/>
       <c r="G65" s="1">
-        <v>144</v>
-      </c>
-      <c r="H65" s="1"/>
+        <v>143</v>
+      </c>
+      <c r="H65" s="8"/>
       <c r="I65" s="8"/>
     </row>
-    <row r="66" spans="1:9" ht="15.75">
+    <row r="66" spans="1:9">
       <c r="A66" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B66" s="1">
         <v>65</v>
       </c>
-      <c r="C66" s="9" t="s">
-        <v>20</v>
+      <c r="C66" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
@@ -3743,10 +3849,14 @@
       <c r="E66" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="G66" s="1">
-        <v>118</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="I66" s="8"/>
     </row>
     <row r="67" spans="1:9" ht="15.75">
       <c r="A67" s="7" t="s">
@@ -3756,7 +3866,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D67" s="1">
         <v>1</v>
@@ -3769,27 +3879,25 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" ht="15.75">
       <c r="A68" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B68" s="1">
         <v>67</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>53</v>
+      <c r="C68" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F68" s="1"/>
       <c r="G68" s="1">
-        <v>1</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3800,19 +3908,19 @@
         <v>68</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>76</v>
+        <v>14</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="G69" s="1">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3823,20 +3931,19 @@
         <v>69</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D70" s="4">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F70" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="G70" s="1">
-        <v>150</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3847,19 +3954,20 @@
         <v>70</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="1">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="D71" s="4">
+        <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F71" s="1"/>
       <c r="G71" s="1">
-        <v>184</v>
+        <v>150</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3870,17 +3978,19 @@
         <v>71</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F72" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="G72" s="1">
-        <v>157</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3891,16 +4001,17 @@
         <v>72</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D73" s="4">
-        <v>0</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="E73" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F73" s="1"/>
       <c r="G73" s="1">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3913,11 +4024,11 @@
       <c r="C74" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D74" s="1">
-        <v>1</v>
+      <c r="D74" s="4">
+        <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="G74" s="1">
         <v>139</v>
@@ -3931,16 +4042,16 @@
         <v>74</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" s="4">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="G75" s="1">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3953,11 +4064,11 @@
       <c r="C76" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="1">
-        <v>1</v>
+      <c r="D76" s="4">
+        <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="G76" s="1">
         <v>185</v>
@@ -3971,16 +4082,16 @@
         <v>76</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G77" s="1">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3991,19 +4102,16 @@
         <v>77</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D78" s="4">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="G78" s="1">
-        <v>205</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>78</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4016,14 +4124,17 @@
       <c r="C79" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D79" s="1">
-        <v>1</v>
+      <c r="D79" s="4">
+        <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="G79" s="1">
-        <v>214</v>
+        <v>205</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4034,7 +4145,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -4054,16 +4165,16 @@
         <v>80</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D81" s="1">
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G81" s="1">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -4074,7 +4185,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D82" s="1">
         <v>1</v>
@@ -4083,7 +4194,7 @@
         <v>9</v>
       </c>
       <c r="G82" s="1">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -4103,31 +4214,30 @@
         <v>9</v>
       </c>
       <c r="G83" s="1">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="13" t="s">
-        <v>80</v>
+      <c r="A84" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B84" s="1">
         <v>83</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D84" s="4">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F84" s="1"/>
+        <v>9</v>
+      </c>
       <c r="G84" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="15.75">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="13" t="s">
         <v>80</v>
       </c>
@@ -4135,23 +4245,20 @@
         <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D85" s="1">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="D85" s="4">
+        <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>52</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F85" s="1"/>
       <c r="G85" s="1">
-        <v>12</v>
-      </c>
-      <c r="H85" s="2"/>
-    </row>
-    <row r="86" spans="1:8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15.75">
       <c r="A86" s="13" t="s">
         <v>80</v>
       </c>
@@ -4159,7 +4266,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="D86" s="1">
         <v>1</v>
@@ -4167,11 +4274,11 @@
       <c r="E86" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>83</v>
+      <c r="F86" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="G86" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H86" s="2"/>
     </row>
@@ -4183,7 +4290,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="D87" s="1">
         <v>1</v>
@@ -4191,9 +4298,11 @@
       <c r="E87" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="G87" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H87" s="2"/>
     </row>
@@ -4205,7 +4314,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
@@ -4215,7 +4324,7 @@
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H88" s="2"/>
     </row>
@@ -4227,7 +4336,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D89" s="1">
         <v>1</v>
@@ -4237,7 +4346,7 @@
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H89" s="2"/>
     </row>
@@ -4249,17 +4358,17 @@
         <v>89</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="D90" s="1">
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H90" s="2"/>
     </row>
@@ -4277,15 +4386,15 @@
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="1:8" ht="15.75">
+    <row r="92" spans="1:8">
       <c r="A92" s="13" t="s">
         <v>80</v>
       </c>
@@ -4293,7 +4402,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
@@ -4303,11 +4412,11 @@
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" ht="15.75">
       <c r="A93" s="13" t="s">
         <v>80</v>
       </c>
@@ -4315,17 +4424,17 @@
         <v>92</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D93" s="4">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="D93" s="1">
+        <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H93" s="2"/>
     </row>
@@ -4337,17 +4446,17 @@
         <v>93</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D94" s="1">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D94" s="4">
+        <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H94" s="2"/>
     </row>
@@ -4359,17 +4468,17 @@
         <v>94</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H95" s="2"/>
     </row>
@@ -4387,11 +4496,11 @@
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H96" s="2"/>
     </row>
@@ -4413,7 +4522,7 @@
       </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H97" s="2"/>
     </row>
@@ -4425,7 +4534,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
@@ -4435,7 +4544,7 @@
       </c>
       <c r="F98" s="1"/>
       <c r="G98" s="1">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H98" s="2"/>
     </row>
@@ -4447,7 +4556,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D99" s="1">
         <v>1</v>
@@ -4457,11 +4566,11 @@
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:9" ht="15.75">
+    <row r="100" spans="1:9">
       <c r="A100" s="13" t="s">
         <v>80</v>
       </c>
@@ -4469,17 +4578,17 @@
         <v>99</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="D100" s="1">
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H100" s="2"/>
     </row>
@@ -4497,15 +4606,15 @@
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" ht="15.75">
       <c r="A102" s="13" t="s">
         <v>80</v>
       </c>
@@ -4513,7 +4622,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D102" s="1">
         <v>1</v>
@@ -4523,7 +4632,7 @@
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H102" s="2"/>
     </row>
@@ -4535,7 +4644,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D103" s="1">
         <v>1</v>
@@ -4557,7 +4666,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="D104" s="1">
         <v>1</v>
@@ -4567,7 +4676,7 @@
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H104" s="2"/>
     </row>
@@ -4579,7 +4688,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D105" s="1">
         <v>1</v>
@@ -4587,14 +4696,11 @@
       <c r="E105" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F105" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="F105" s="1"/>
       <c r="G105" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H105" s="2"/>
-      <c r="I105" s="14"/>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="13" t="s">
@@ -4604,7 +4710,7 @@
         <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D106" s="1">
         <v>1</v>
@@ -4613,7 +4719,7 @@
         <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G106" s="1">
         <v>55</v>
@@ -4621,15 +4727,15 @@
       <c r="H106" s="2"/>
       <c r="I106" s="14"/>
     </row>
-    <row r="107" spans="1:9" ht="15.75">
+    <row r="107" spans="1:9">
       <c r="A107" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B107" s="1">
         <v>106</v>
       </c>
-      <c r="C107" s="9" t="s">
-        <v>62</v>
+      <c r="C107" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="D107" s="1">
         <v>1</v>
@@ -4637,24 +4743,24 @@
       <c r="E107" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F107" s="9" t="s">
-        <v>63</v>
+      <c r="F107" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G107" s="1">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="14"/>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" ht="15.75">
       <c r="A108" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B108" s="1">
         <v>107</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>61</v>
+      <c r="C108" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="D108" s="1">
         <v>1</v>
@@ -4662,9 +4768,11 @@
       <c r="E108" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F108" s="1"/>
+      <c r="F108" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="G108" s="1">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H108" s="2"/>
       <c r="I108" s="14"/>
@@ -4677,7 +4785,7 @@
         <v>108</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D109" s="1">
         <v>1</v>
@@ -4687,10 +4795,10 @@
       </c>
       <c r="F109" s="1"/>
       <c r="G109" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H109" s="2"/>
-      <c r="I109" s="15"/>
+      <c r="I109" s="14"/>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="13" t="s">
@@ -4706,13 +4814,14 @@
         <v>1</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F110" s="1"/>
       <c r="G110" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H110" s="2"/>
+      <c r="I110" s="15"/>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="13" t="s">
@@ -4722,17 +4831,17 @@
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="D111" s="1">
         <v>1</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F111" s="1"/>
       <c r="G111" s="1">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H111" s="2"/>
     </row>
@@ -4744,7 +4853,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112" s="1">
         <v>1</v>
@@ -4766,7 +4875,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D113" s="1">
         <v>1</v>
@@ -4788,7 +4897,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D114" s="1">
         <v>1</v>
@@ -4810,17 +4919,17 @@
         <v>114</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D115" s="1">
         <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H115" s="2"/>
     </row>
@@ -4832,7 +4941,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D116" s="1">
         <v>1</v>
@@ -4846,25 +4955,25 @@
       </c>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8" ht="15.75">
+    <row r="117" spans="1:8">
       <c r="A117" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B117" s="1">
         <v>116</v>
       </c>
-      <c r="C117" s="9" t="s">
-        <v>64</v>
+      <c r="C117" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D117" s="1">
         <v>1</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="F117" s="1"/>
       <c r="G117" s="1">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H117" s="2"/>
     </row>
@@ -4876,7 +4985,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D118" s="1">
         <v>1</v>
@@ -4886,19 +4995,19 @@
       </c>
       <c r="F118" s="1"/>
       <c r="G118" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" ht="15.75">
       <c r="A119" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B119" s="1">
         <v>118</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>68</v>
+      <c r="C119" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="D119" s="1">
         <v>1</v>
@@ -4907,8 +5016,8 @@
         <v>9</v>
       </c>
       <c r="F119" s="1"/>
-      <c r="G119" s="16">
-        <v>81</v>
+      <c r="G119" s="1">
+        <v>79</v>
       </c>
       <c r="H119" s="2"/>
     </row>
@@ -4920,7 +5029,7 @@
         <v>119</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D120" s="1">
         <v>1</v>
@@ -4930,7 +5039,7 @@
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="16">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H120" s="2"/>
     </row>
@@ -4942,7 +5051,7 @@
         <v>120</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="D121" s="1">
         <v>1</v>
@@ -4952,7 +5061,7 @@
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="16">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H121" s="2"/>
     </row>
@@ -4964,17 +5073,17 @@
         <v>121</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D122" s="1">
         <v>1</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="16">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H122" s="2"/>
     </row>
@@ -4986,17 +5095,17 @@
         <v>122</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="D123" s="1">
         <v>1</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="16">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H123" s="2"/>
     </row>
@@ -5008,7 +5117,7 @@
         <v>123</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="D124" s="1">
         <v>1</v>
@@ -5016,11 +5125,9 @@
       <c r="E124" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F124" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="F124" s="1"/>
       <c r="G124" s="16">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H124" s="2"/>
     </row>
@@ -5032,7 +5139,7 @@
         <v>124</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D125" s="1">
         <v>1</v>
@@ -5056,7 +5163,7 @@
         <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D126" s="1">
         <v>1</v>
@@ -5080,17 +5187,19 @@
         <v>126</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D127" s="4">
-        <v>0</v>
+        <v>105</v>
+      </c>
+      <c r="D127" s="1">
+        <v>1</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1">
-        <v>91</v>
+        <v>9</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G127" s="16">
+        <v>90</v>
       </c>
       <c r="H127" s="2"/>
     </row>
@@ -5102,17 +5211,17 @@
         <v>127</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D128" s="1">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="D128" s="4">
+        <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F128" s="1"/>
       <c r="G128" s="1">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H128" s="2"/>
     </row>
@@ -5124,17 +5233,17 @@
         <v>128</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="D129" s="1">
         <v>1</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="F129" s="1"/>
       <c r="G129" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H129" s="2"/>
     </row>
@@ -5146,17 +5255,17 @@
         <v>129</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D130" s="1">
         <v>1</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>9</v>
+        <v>210</v>
       </c>
       <c r="F130" s="1"/>
       <c r="G130" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H130" s="2"/>
     </row>
@@ -5168,7 +5277,7 @@
         <v>130</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="D131" s="1">
         <v>1</v>
@@ -5176,11 +5285,9 @@
       <c r="E131" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="F131" s="1"/>
       <c r="G131" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H131" s="2"/>
     </row>
@@ -5192,7 +5299,7 @@
         <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D132" s="1">
         <v>1</v>
@@ -5201,14 +5308,14 @@
         <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G132" s="1">
         <v>99</v>
       </c>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" ht="15.75">
+    <row r="133" spans="1:8">
       <c r="A133" s="13" t="s">
         <v>80</v>
       </c>
@@ -5216,7 +5323,7 @@
         <v>132</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D133" s="1">
         <v>1</v>
@@ -5225,14 +5332,14 @@
         <v>9</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G133" s="1">
         <v>99</v>
       </c>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" ht="15.75">
       <c r="A134" s="13" t="s">
         <v>80</v>
       </c>
@@ -5240,7 +5347,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D134" s="1">
         <v>1</v>
@@ -5249,7 +5356,7 @@
         <v>9</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G134" s="1">
         <v>99</v>
@@ -5264,7 +5371,7 @@
         <v>134</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D135" s="1">
         <v>1</v>
@@ -5272,9 +5379,11 @@
       <c r="E135" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F135" s="1"/>
+      <c r="F135" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G135" s="1">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H135" s="2"/>
     </row>
@@ -5286,7 +5395,7 @@
         <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="D136" s="1">
         <v>1</v>
@@ -5296,7 +5405,7 @@
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H136" s="2"/>
     </row>
@@ -5308,7 +5417,7 @@
         <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="D137" s="1">
         <v>1</v>
@@ -5330,17 +5439,17 @@
         <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="D138" s="1">
         <v>1</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="1">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H138" s="2"/>
     </row>
@@ -5352,17 +5461,17 @@
         <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="D139" s="1">
         <v>1</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H139" s="2"/>
     </row>
@@ -5374,7 +5483,7 @@
         <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="D140" s="1">
         <v>1</v>
@@ -5384,7 +5493,7 @@
       </c>
       <c r="F140" s="1"/>
       <c r="G140" s="1">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H140" s="2"/>
     </row>
@@ -5396,17 +5505,17 @@
         <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D141" s="4">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="D141" s="1">
+        <v>1</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F141" s="1"/>
-      <c r="G141" s="1" t="s">
-        <v>119</v>
+      <c r="G141" s="1">
+        <v>124</v>
       </c>
       <c r="H141" s="2"/>
     </row>
@@ -5418,7 +5527,7 @@
         <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D142" s="4">
         <v>0</v>
@@ -5428,7 +5537,7 @@
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H142" s="2"/>
     </row>
@@ -5440,7 +5549,7 @@
         <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="D143" s="4">
         <v>0</v>
@@ -5450,7 +5559,7 @@
       </c>
       <c r="F143" s="1"/>
       <c r="G143" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H143" s="2"/>
     </row>
@@ -5462,7 +5571,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D144" s="4">
         <v>0</v>
@@ -5472,7 +5581,7 @@
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H144" s="2"/>
     </row>
@@ -5484,7 +5593,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D145" s="4">
         <v>0</v>
@@ -5492,11 +5601,9 @@
       <c r="E145" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F145" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G145" s="1">
-        <v>136</v>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="H145" s="2"/>
     </row>
@@ -5508,19 +5615,19 @@
         <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D146" s="1">
-        <v>1</v>
+        <v>120</v>
+      </c>
+      <c r="D146" s="4">
+        <v>0</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="G146" s="1">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H146" s="2"/>
     </row>
@@ -5532,17 +5639,19 @@
         <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D147" s="1">
         <v>1</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F147" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="G147" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H147" s="2"/>
     </row>
@@ -5554,17 +5663,17 @@
         <v>147</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D148" s="1">
         <v>1</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H148" s="2"/>
     </row>
@@ -5575,8 +5684,8 @@
       <c r="B149" s="1">
         <v>148</v>
       </c>
-      <c r="C149" s="17" t="s">
-        <v>31</v>
+      <c r="C149" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D149" s="1">
         <v>1</v>
@@ -5600,8 +5709,8 @@
       <c r="C150" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D150" s="4">
-        <v>0</v>
+      <c r="D150" s="1">
+        <v>1</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>100</v>
@@ -5619,18 +5728,18 @@
       <c r="B151" s="1">
         <v>150</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D151" s="1">
-        <v>1</v>
+      <c r="C151" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D151" s="4">
+        <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F151" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="F151" s="1"/>
       <c r="G151" s="1">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="H151" s="2"/>
     </row>
@@ -5642,20 +5751,19 @@
         <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D152" s="1">
         <v>1</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F152" s="2"/>
       <c r="G152" s="1">
-        <v>1</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H152" s="2"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="13" t="s">
@@ -5665,17 +5773,19 @@
         <v>152</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="D153" s="1">
         <v>1</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F153" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="G153" s="1">
-        <v>177</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5686,17 +5796,17 @@
         <v>153</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D154" s="1">
         <v>1</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154" s="1">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5707,19 +5817,17 @@
         <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D155" s="4">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="D155" s="1">
+        <v>1</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F155" s="1"/>
       <c r="G155" s="1">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5730,17 +5838,19 @@
         <v>155</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D156" s="1">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="D156" s="4">
+        <v>0</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F156" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="G156" s="1">
-        <v>157</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5751,17 +5861,17 @@
         <v>156</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D157" s="4">
-        <v>0</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="D157" s="1">
+        <v>1</v>
+      </c>
+      <c r="E157" s="29" t="s">
+        <v>209</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5774,11 +5884,11 @@
       <c r="C158" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D158" s="1">
-        <v>1</v>
+      <c r="D158" s="4">
+        <v>0</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1">
@@ -5799,10 +5909,11 @@
         <v>1</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F159" s="1"/>
       <c r="G159" s="1">
-        <v>77</v>
+        <v>166</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5813,22 +5924,19 @@
         <v>159</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D160" s="4">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="D160" s="1">
+        <v>1</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G160" s="1">
         <v>77</v>
       </c>
-      <c r="G160" s="1">
-        <v>156</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" s="13" t="s">
         <v>80</v>
       </c>
@@ -5836,19 +5944,22 @@
         <v>160</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D161" s="4">
         <v>0</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="G161" s="1">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
+        <v>156</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="13" t="s">
         <v>80</v>
       </c>
@@ -5856,20 +5967,19 @@
         <v>161</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D162" s="1">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D162" s="4">
+        <v>0</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F162" s="1"/>
+        <v>28</v>
+      </c>
       <c r="G162" s="1">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163" s="13" t="s">
         <v>80</v>
       </c>
@@ -5883,14 +5993,14 @@
         <v>1</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1">
         <v>189</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:8">
       <c r="A164" s="13" t="s">
         <v>80</v>
       </c>
@@ -5898,7 +6008,7 @@
         <v>163</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D164" s="1">
         <v>1</v>
@@ -5906,11 +6016,12 @@
       <c r="E164" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F164" s="1"/>
       <c r="G164" s="1">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165" s="13" t="s">
         <v>80</v>
       </c>
@@ -5924,13 +6035,13 @@
         <v>1</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G165" s="1">
         <v>192</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:8">
       <c r="A166" s="13" t="s">
         <v>80</v>
       </c>
@@ -5944,13 +6055,13 @@
         <v>1</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G166" s="1">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167" s="13" t="s">
         <v>80</v>
       </c>
@@ -5958,19 +6069,19 @@
         <v>166</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D167" s="4">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="D167" s="1">
+        <v>1</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G167" s="1">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="13" t="s">
         <v>80</v>
       </c>
@@ -5980,17 +6091,17 @@
       <c r="C168" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D168" s="1">
-        <v>1</v>
+      <c r="D168" s="4">
+        <v>0</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G168" s="1">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="13" t="s">
         <v>80</v>
       </c>
@@ -5998,7 +6109,7 @@
         <v>168</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="D169" s="1">
         <v>1</v>
@@ -6007,10 +6118,10 @@
         <v>28</v>
       </c>
       <c r="G169" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="13" t="s">
         <v>80</v>
       </c>
@@ -6018,20 +6129,19 @@
         <v>169</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="D170" s="1">
         <v>1</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F170" s="2"/>
+        <v>28</v>
+      </c>
       <c r="G170" s="1">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" s="13" t="s">
         <v>80</v>
       </c>
@@ -6039,19 +6149,20 @@
         <v>170</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="D171" s="1">
         <v>1</v>
       </c>
-      <c r="E171" s="2" t="s">
-        <v>128</v>
-      </c>
+      <c r="E171" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F171" s="2"/>
       <c r="G171" s="1">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" s="13" t="s">
         <v>80</v>
       </c>
@@ -6059,19 +6170,19 @@
         <v>171</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D172" s="4">
-        <v>0</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>9</v>
+        <v>126</v>
+      </c>
+      <c r="D172" s="1">
+        <v>1</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="G172" s="1">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" s="13" t="s">
         <v>80</v>
       </c>
@@ -6081,8 +6192,8 @@
       <c r="C173" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D173" s="1">
-        <v>1</v>
+      <c r="D173" s="4">
+        <v>0</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>9</v>
@@ -6091,7 +6202,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:8">
       <c r="A174" s="13" t="s">
         <v>80</v>
       </c>
@@ -6111,7 +6222,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:8">
       <c r="A175" s="13" t="s">
         <v>80</v>
       </c>
@@ -6125,13 +6236,13 @@
         <v>1</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="G175" s="1">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="13" t="s">
         <v>80</v>
       </c>
@@ -6145,13 +6256,13 @@
         <v>1</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="G176" s="1">
         <v>239</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:10">
       <c r="A177" s="13" t="s">
         <v>80</v>
       </c>
@@ -6159,22 +6270,19 @@
         <v>176</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D177" s="4">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="D177" s="1">
+        <v>1</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="G177" s="1">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
       <c r="A178" s="13" t="s">
         <v>80</v>
       </c>
@@ -6182,7 +6290,7 @@
         <v>177</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="D178" s="4">
         <v>0</v>
@@ -6190,12 +6298,14 @@
       <c r="E178" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F178" s="1"/>
+      <c r="F178" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="G178" s="1">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
       <c r="A179" s="13" t="s">
         <v>80</v>
       </c>
@@ -6205,251 +6315,239 @@
       <c r="C179" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D179" s="1">
-        <v>1</v>
+      <c r="D179" s="4">
+        <v>0</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="F179" s="1"/>
       <c r="G179" s="1">
         <v>175</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75">
-      <c r="A180" s="18" t="s">
-        <v>132</v>
+    <row r="180" spans="1:10">
+      <c r="A180" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="B180" s="1">
         <v>179</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="D180" s="1">
         <v>1</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="F180" s="1"/>
       <c r="G180" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9">
-      <c r="A181" s="18" t="s">
-        <v>132</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="B181" s="1">
         <v>180</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D181" s="1">
-        <v>1</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F181" s="2"/>
-      <c r="G181" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9">
-      <c r="A182" s="18" t="s">
-        <v>132</v>
+      <c r="C181" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D181" s="30">
+        <v>0</v>
+      </c>
+      <c r="E181" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F181" s="30"/>
+      <c r="G181" s="30">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="B182" s="1">
         <v>181</v>
       </c>
-      <c r="C182" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D182" s="4">
-        <v>0</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F182" s="2"/>
-      <c r="G182" s="1">
-        <v>222</v>
-      </c>
-      <c r="H182" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9">
+      <c r="C182" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="D182" s="30">
+        <v>1</v>
+      </c>
+      <c r="E182" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F182" s="30"/>
+      <c r="G182" s="30">
+        <v>242</v>
+      </c>
+      <c r="J182" s="1"/>
+    </row>
+    <row r="183" spans="1:10" ht="15.75">
       <c r="A183" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B183" s="1">
         <v>182</v>
       </c>
-      <c r="C183" s="2" t="s">
-        <v>37</v>
+      <c r="C183" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="D183" s="1">
         <v>1</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F183" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="F183" s="1"/>
       <c r="G183" s="1">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9">
+        <v>44</v>
+      </c>
+      <c r="J183" s="33"/>
+    </row>
+    <row r="184" spans="1:10">
       <c r="A184" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B184" s="1">
         <v>183</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>37</v>
+      <c r="C184" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D184" s="1">
         <v>1</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G184" s="1">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" ht="15.75">
-      <c r="A185" s="19" t="s">
-        <v>135</v>
+        <v>14</v>
+      </c>
+      <c r="F184" s="2"/>
+      <c r="G184" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="B185" s="1">
         <v>184</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D185" s="1">
-        <v>1</v>
+      <c r="C185" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D185" s="4">
+        <v>0</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F185" s="9" t="s">
-        <v>52</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F185" s="2"/>
       <c r="G185" s="1">
-        <v>12</v>
-      </c>
-      <c r="H185" s="8"/>
-    </row>
-    <row r="186" spans="1:9">
-      <c r="A186" s="19" t="s">
-        <v>135</v>
+        <v>222</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="B186" s="1">
         <v>185</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>81</v>
+      <c r="C186" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D186" s="1">
         <v>1</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F186" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="F186" s="2"/>
       <c r="G186" s="1">
-        <v>14</v>
-      </c>
-      <c r="H186" s="8"/>
-      <c r="I186" s="8"/>
-    </row>
-    <row r="187" spans="1:9">
-      <c r="A187" s="19" t="s">
-        <v>135</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="B187" s="1">
         <v>186</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D187" s="4">
-        <v>0</v>
+      <c r="C187" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D187" s="1">
+        <v>1</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F187" s="1"/>
+        <v>32</v>
+      </c>
       <c r="G187" s="1">
-        <v>42</v>
-      </c>
-      <c r="H187" s="8"/>
-      <c r="I187" s="8"/>
-    </row>
-    <row r="188" spans="1:9">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="15.75">
       <c r="A188" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B188" s="1">
         <v>187</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D188" s="4">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="D188" s="1">
+        <v>1</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F188" s="20" t="s">
-        <v>137</v>
+      <c r="F188" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="G188" s="1">
-        <v>55</v>
-      </c>
-      <c r="H188" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I188" s="8"/>
-    </row>
-    <row r="189" spans="1:9">
+        <v>12</v>
+      </c>
+      <c r="H188" s="8"/>
+    </row>
+    <row r="189" spans="1:10">
       <c r="A189" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B189" s="1">
         <v>188</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D189" s="4">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="D189" s="1">
+        <v>1</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F189" s="20" t="s">
-        <v>140</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F189" s="1"/>
       <c r="G189" s="1">
-        <v>55</v>
-      </c>
-      <c r="H189" s="8" t="s">
-        <v>138</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H189" s="8"/>
       <c r="I189" s="8"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:10">
       <c r="A190" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B190" s="1">
         <v>189</v>
@@ -6457,53 +6555,55 @@
       <c r="C190" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D190" s="1">
-        <v>1</v>
+      <c r="D190" s="4">
+        <v>0</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F190" s="1"/>
       <c r="G190" s="1">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H190" s="8"/>
       <c r="I190" s="8"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:10">
       <c r="A191" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B191" s="1">
         <v>190</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="D191" s="4">
         <v>0</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>104</v>
+        <v>9</v>
+      </c>
+      <c r="F191" s="20" t="s">
+        <v>135</v>
       </c>
       <c r="G191" s="1">
-        <v>64</v>
-      </c>
-      <c r="H191" s="21"/>
+        <v>55</v>
+      </c>
+      <c r="H191" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="I191" s="8"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:10">
       <c r="A192" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B192" s="1">
         <v>191</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D192" s="4">
         <v>0</v>
@@ -6511,22 +6611,26 @@
       <c r="E192" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F192" s="1"/>
+      <c r="F192" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="G192" s="1">
-        <v>65</v>
-      </c>
-      <c r="H192" s="8"/>
+        <v>55</v>
+      </c>
+      <c r="H192" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="I192" s="8"/>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B193" s="1">
         <v>192</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D193" s="1">
         <v>1</v>
@@ -6536,137 +6640,139 @@
       </c>
       <c r="F193" s="1"/>
       <c r="G193" s="1">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H193" s="8"/>
       <c r="I193" s="8"/>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B194" s="1">
         <v>193</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D194" s="1">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D194" s="4">
+        <v>0</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F194" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="G194" s="1">
-        <v>87</v>
-      </c>
-      <c r="H194" s="8"/>
+        <v>64</v>
+      </c>
+      <c r="H194" s="21"/>
       <c r="I194" s="8"/>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B195" s="1">
         <v>194</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="D195" s="4">
         <v>0</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="F195" s="1"/>
-      <c r="G195" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="G195" s="1">
+        <v>65</v>
+      </c>
+      <c r="H195" s="8"/>
       <c r="I195" s="8"/>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B196" s="1">
         <v>195</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D196" s="1">
         <v>1</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F196" s="1"/>
       <c r="G196" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H196" s="8"/>
       <c r="I196" s="8"/>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B197" s="1">
         <v>196</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D197" s="1">
         <v>1</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="F197" s="1"/>
       <c r="G197" s="1">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="H197" s="8"/>
       <c r="I197" s="8"/>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B198" s="1">
         <v>197</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D198" s="1">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="D198" s="4">
+        <v>0</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="F198" s="1"/>
-      <c r="G198" s="1">
-        <v>100</v>
-      </c>
-      <c r="H198" s="8"/>
+      <c r="G198" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="I198" s="8"/>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B199" s="1">
         <v>198</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="D199" s="1">
         <v>1</v>
@@ -6683,13 +6789,13 @@
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B200" s="1">
         <v>199</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="D200" s="1">
         <v>1</v>
@@ -6706,16 +6812,16 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B201" s="1">
         <v>200</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D201" s="4">
-        <v>0</v>
+        <v>142</v>
+      </c>
+      <c r="D201" s="1">
+        <v>1</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>32</v>
@@ -6729,266 +6835,266 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B202" s="1">
         <v>201</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D202" s="1">
         <v>1</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F202" s="1"/>
       <c r="G202" s="1">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H202" s="8"/>
       <c r="I202" s="8"/>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B203" s="1">
         <v>202</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="D203" s="1">
         <v>1</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203" s="1">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="H203" s="8"/>
       <c r="I203" s="8"/>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B204" s="1">
         <v>203</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D204" s="1">
+        <v>123</v>
+      </c>
+      <c r="D204" s="30">
         <v>1</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204" s="1">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="H204" s="8"/>
       <c r="I204" s="8"/>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B205" s="1">
         <v>204</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="D205" s="1">
         <v>1</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F205" s="1"/>
       <c r="G205" s="1">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H205" s="8"/>
       <c r="I205" s="8"/>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B206" s="1">
         <v>205</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="D206" s="1">
         <v>1</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F206" s="1"/>
       <c r="G206" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H206" s="8"/>
       <c r="I206" s="8"/>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B207" s="1">
         <v>206</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="D207" s="1">
         <v>1</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F207" s="1"/>
       <c r="G207" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H207" s="8"/>
       <c r="I207" s="8"/>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B208" s="1">
         <v>207</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="D208" s="1">
         <v>1</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="F208" s="1"/>
       <c r="G208" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H208" s="8"/>
       <c r="I208" s="8"/>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B209" s="1">
         <v>208</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D209" s="1">
         <v>1</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="F209" s="1"/>
       <c r="G209" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H209" s="8"/>
       <c r="I209" s="8"/>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B210" s="1">
         <v>209</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="D210" s="1">
         <v>1</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="F210" s="1"/>
       <c r="G210" s="1">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H210" s="8"/>
       <c r="I210" s="8"/>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B211" s="1">
         <v>210</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="D211" s="1">
         <v>1</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="F211" s="1"/>
       <c r="G211" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H211" s="8"/>
       <c r="I211" s="8"/>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B212" s="1">
         <v>211</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="D212" s="1">
         <v>1</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F212" s="1"/>
       <c r="G212" s="1">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H212" s="8"/>
       <c r="I212" s="8"/>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B213" s="1">
         <v>212</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D213" s="1">
         <v>1</v>
@@ -6998,43 +7104,43 @@
       </c>
       <c r="F213" s="1"/>
       <c r="G213" s="1">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H213" s="8"/>
       <c r="I213" s="8"/>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B214" s="1">
         <v>213</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="D214" s="1">
         <v>1</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F214" s="1"/>
       <c r="G214" s="1">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="H214" s="8"/>
       <c r="I214" s="8"/>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B215" s="1">
         <v>214</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D215" s="1">
         <v>1</v>
@@ -7044,20 +7150,20 @@
       </c>
       <c r="F215" s="1"/>
       <c r="G215" s="1">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H215" s="8"/>
       <c r="I215" s="8"/>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B216" s="1">
         <v>215</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D216" s="1">
         <v>1</v>
@@ -7067,20 +7173,20 @@
       </c>
       <c r="F216" s="1"/>
       <c r="G216" s="1">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H216" s="8"/>
       <c r="I216" s="8"/>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B217" s="1">
         <v>216</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D217" s="1">
         <v>1</v>
@@ -7090,43 +7196,43 @@
       </c>
       <c r="F217" s="1"/>
       <c r="G217" s="1">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="H217" s="8"/>
       <c r="I217" s="8"/>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B218" s="1">
         <v>217</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="D218" s="1">
         <v>1</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="F218" s="1"/>
       <c r="G218" s="1">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="H218" s="8"/>
       <c r="I218" s="8"/>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B219" s="1">
         <v>218</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="D219" s="1">
         <v>1</v>
@@ -7136,187 +7242,191 @@
       </c>
       <c r="F219" s="1"/>
       <c r="G219" s="1">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="H219" s="8"/>
       <c r="I219" s="8"/>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B220" s="1">
         <v>219</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="D220" s="1">
         <v>1</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="F220" s="1"/>
       <c r="G220" s="1">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H220" s="8"/>
       <c r="I220" s="8"/>
     </row>
-    <row r="221" spans="1:9" ht="15.75">
+    <row r="221" spans="1:9">
       <c r="A221" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B221" s="1">
         <v>220</v>
       </c>
-      <c r="C221" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D221" s="8">
+      <c r="C221" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D221" s="1">
         <v>1</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F221" s="1"/>
       <c r="G221" s="1">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="H221" s="8"/>
       <c r="I221" s="8"/>
     </row>
-    <row r="222" spans="1:9" ht="15.75">
+    <row r="222" spans="1:9">
       <c r="A222" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B222" s="1">
         <v>221</v>
       </c>
-      <c r="C222" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D222" s="8">
+      <c r="C222" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D222" s="1">
         <v>1</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F222" s="1"/>
       <c r="G222" s="1">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="H222" s="8"/>
       <c r="I222" s="8"/>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B223" s="1">
         <v>222</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="D223" s="1">
         <v>1</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F223" s="1"/>
       <c r="G223" s="1">
-        <v>101</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="H223" s="8"/>
       <c r="I223" s="8"/>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" ht="15.75">
       <c r="A224" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B224" s="1">
         <v>223</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D224" s="1">
+      <c r="C224" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D224" s="8">
         <v>1</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="G224" s="1">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8">
+        <v>78</v>
+      </c>
+      <c r="H224" s="8"/>
+      <c r="I224" s="8"/>
+    </row>
+    <row r="225" spans="1:9" ht="15.75">
       <c r="A225" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B225" s="1">
         <v>224</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D225" s="4">
-        <v>0</v>
+      <c r="C225" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D225" s="8">
+        <v>1</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F225" s="1"/>
+        <v>9</v>
+      </c>
       <c r="G225" s="1">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8">
+        <v>79</v>
+      </c>
+      <c r="H225" s="8"/>
+      <c r="I225" s="8"/>
+    </row>
+    <row r="226" spans="1:9">
       <c r="A226" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B226" s="1">
         <v>225</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D226" s="1">
         <v>1</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F226" s="1"/>
+        <v>14</v>
+      </c>
       <c r="G226" s="1">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8">
+        <v>101</v>
+      </c>
+      <c r="I226" s="8"/>
+    </row>
+    <row r="227" spans="1:9">
       <c r="A227" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B227" s="1">
         <v>226</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D227" s="4">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="D227" s="1">
+        <v>1</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="G227" s="1">
-        <v>159</v>
-      </c>
-      <c r="H227" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
       <c r="A228" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B228" s="1">
         <v>227</v>
@@ -7330,45 +7440,42 @@
       <c r="E228" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="F228" s="1"/>
       <c r="G228" s="1">
-        <v>186</v>
-      </c>
-      <c r="H228" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
       <c r="A229" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B229" s="1">
         <v>228</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D229" s="4">
-        <v>0</v>
-      </c>
-      <c r="E229" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D229" s="1">
+        <v>1</v>
+      </c>
+      <c r="E229" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F229" s="1"/>
       <c r="G229" s="1">
-        <v>186</v>
-      </c>
-      <c r="H229" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8">
+        <v>157</v>
+      </c>
+      <c r="I229" s="31"/>
+    </row>
+    <row r="230" spans="1:9">
       <c r="A230" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B230" s="1">
         <v>229</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D230" s="4">
         <v>0</v>
@@ -7377,21 +7484,21 @@
         <v>77</v>
       </c>
       <c r="G230" s="1">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:9">
       <c r="A231" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B231" s="1">
         <v>230</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D231" s="4">
         <v>0</v>
@@ -7400,41 +7507,44 @@
         <v>77</v>
       </c>
       <c r="G231" s="1">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="H231" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:9">
       <c r="A232" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B232" s="1">
         <v>231</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D232" s="1">
-        <v>1</v>
+        <v>148</v>
+      </c>
+      <c r="D232" s="4">
+        <v>0</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="G232" s="1">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8">
+        <v>186</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
       <c r="A233" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B233" s="1">
         <v>232</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="D233" s="4">
         <v>0</v>
@@ -7443,78 +7553,84 @@
         <v>77</v>
       </c>
       <c r="G233" s="1">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8">
+        <v>188</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
       <c r="A234" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B234" s="1">
         <v>233</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D234" s="1">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="D234" s="4">
+        <v>0</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="G234" s="1">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8">
+        <v>130</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
       <c r="A235" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B235" s="1">
         <v>234</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D235" s="1">
         <v>1</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G235" s="1">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8">
+        <v>32</v>
+      </c>
+      <c r="G235" s="30">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
       <c r="A236" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B236" s="1">
         <v>235</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D236" s="1">
-        <v>1</v>
+        <v>106</v>
+      </c>
+      <c r="D236" s="4">
+        <v>0</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="G236" s="1">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
       <c r="A237" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B237" s="1">
         <v>236</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="D237" s="1">
         <v>1</v>
@@ -7523,12 +7639,12 @@
         <v>32</v>
       </c>
       <c r="G237" s="1">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
       <c r="A238" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B238" s="1">
         <v>237</v>
@@ -7540,35 +7656,35 @@
         <v>1</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G238" s="1">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
       <c r="A239" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B239" s="1">
         <v>238</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="D239" s="1">
         <v>1</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="G239" s="1">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
       <c r="A240" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B240" s="1">
         <v>239</v>
@@ -7580,41 +7696,41 @@
         <v>1</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G240" s="1">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B241" s="1">
         <v>240</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D241" s="4">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="D241" s="1">
+        <v>1</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G241" s="1">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="242" spans="1:10">
       <c r="A242" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B242" s="1">
         <v>241</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D242" s="1">
         <v>1</v>
@@ -7623,18 +7739,18 @@
         <v>9</v>
       </c>
       <c r="G242" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="243" spans="1:10">
       <c r="A243" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B243" s="1">
         <v>242</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D243" s="1">
         <v>1</v>
@@ -7648,16 +7764,16 @@
     </row>
     <row r="244" spans="1:10">
       <c r="A244" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B244" s="1">
         <v>243</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D244" s="1">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="D244" s="4">
+        <v>0</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>9</v>
@@ -7668,13 +7784,13 @@
     </row>
     <row r="245" spans="1:10">
       <c r="A245" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B245" s="1">
         <v>244</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="D245" s="1">
         <v>1</v>
@@ -7683,12 +7799,12 @@
         <v>9</v>
       </c>
       <c r="G245" s="1">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="246" spans="1:10">
       <c r="A246" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B246" s="1">
         <v>245</v>
@@ -7703,56 +7819,52 @@
         <v>9</v>
       </c>
       <c r="G246" s="1">
-        <v>234</v>
+        <v>216</v>
       </c>
     </row>
     <row r="247" spans="1:10">
       <c r="A247" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B247" s="1">
         <v>246</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D247" s="4">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="D247" s="1">
+        <v>1</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="G247" s="1">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="248" spans="1:10">
       <c r="A248" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B248" s="1">
         <v>247</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="D248" s="1">
         <v>1</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>155</v>
+        <v>9</v>
       </c>
       <c r="G248" s="1">
-        <v>132</v>
-      </c>
-      <c r="H248" s="2"/>
+        <v>226</v>
+      </c>
     </row>
     <row r="249" spans="1:10">
       <c r="A249" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B249" s="1">
         <v>248</v>
@@ -7764,270 +7876,271 @@
         <v>1</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F249" s="1"/>
+        <v>9</v>
+      </c>
       <c r="G249" s="1">
-        <v>155</v>
-      </c>
-      <c r="H249" s="2"/>
+        <v>234</v>
+      </c>
     </row>
     <row r="250" spans="1:10">
       <c r="A250" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B250" s="1">
         <v>249</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D250" s="1">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="D250" s="4">
+        <v>0</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F250" s="1"/>
+        <v>77</v>
+      </c>
       <c r="G250" s="1">
-        <v>155</v>
-      </c>
-      <c r="H250" s="2"/>
+        <v>236</v>
+      </c>
     </row>
     <row r="251" spans="1:10">
       <c r="A251" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B251" s="1">
         <v>250</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D251" s="4">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="D251" s="1">
+        <v>1</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F251" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>153</v>
+      </c>
       <c r="G251" s="1">
-        <v>126</v>
-      </c>
-      <c r="H251" s="1"/>
-      <c r="I251" s="1"/>
-      <c r="J251" s="1"/>
-    </row>
-    <row r="252" spans="1:10" ht="15.75">
-      <c r="A252" s="22" t="s">
-        <v>157</v>
+        <v>132</v>
+      </c>
+      <c r="H251" s="2"/>
+    </row>
+    <row r="252" spans="1:10">
+      <c r="A252" s="19" t="s">
+        <v>133</v>
       </c>
       <c r="B252" s="1">
         <v>251</v>
       </c>
       <c r="C252" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D252" s="1">
+        <v>1</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F252" s="1"/>
+      <c r="G252" s="1">
+        <v>155</v>
+      </c>
+      <c r="H252" s="2"/>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="A253" s="19" t="s">
         <v>133</v>
-      </c>
-      <c r="D252" s="4">
-        <v>0</v>
-      </c>
-      <c r="E252" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G252" s="1">
-        <v>66</v>
-      </c>
-      <c r="H252" s="2"/>
-    </row>
-    <row r="253" spans="1:10">
-      <c r="A253" s="22" t="s">
-        <v>157</v>
       </c>
       <c r="B253" s="1">
         <v>252</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="D253" s="1">
         <v>1</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F253" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="F253" s="1"/>
       <c r="G253" s="1">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="H253" s="2"/>
     </row>
     <row r="254" spans="1:10">
-      <c r="A254" s="23" t="s">
-        <v>158</v>
+      <c r="A254" s="19" t="s">
+        <v>133</v>
       </c>
       <c r="B254" s="1">
         <v>253</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="D254" s="4">
         <v>0</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F254" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F254" s="1"/>
       <c r="G254" s="1">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="H254" s="1"/>
-    </row>
-    <row r="255" spans="1:10">
-      <c r="A255" s="23" t="s">
-        <v>158</v>
+      <c r="I254" s="1"/>
+      <c r="J254" s="1"/>
+    </row>
+    <row r="255" spans="1:10" ht="18.75">
+      <c r="A255" s="19" t="s">
+        <v>133</v>
       </c>
       <c r="B255" s="1">
         <v>254</v>
       </c>
-      <c r="C255" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D255" s="4">
-        <v>0</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F255" s="1"/>
-      <c r="G255" s="1">
-        <v>11</v>
-      </c>
-      <c r="H255" s="8"/>
-      <c r="I255" s="1"/>
+      <c r="C255" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D255" s="30">
+        <v>1</v>
+      </c>
+      <c r="E255" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F255" s="32"/>
+      <c r="G255" s="30">
+        <v>243</v>
+      </c>
+      <c r="H255" s="2"/>
     </row>
     <row r="256" spans="1:10" ht="15.75">
-      <c r="A256" s="23" t="s">
-        <v>158</v>
+      <c r="A256" s="22" t="s">
+        <v>155</v>
       </c>
       <c r="B256" s="1">
         <v>255</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D256" s="1">
-        <v>1</v>
+        <v>131</v>
+      </c>
+      <c r="D256" s="4">
+        <v>0</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F256" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="G256" s="1">
-        <v>10</v>
-      </c>
-      <c r="H256" s="8"/>
-      <c r="I256" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="H256" s="2"/>
     </row>
     <row r="257" spans="1:9">
-      <c r="A257" s="23" t="s">
-        <v>158</v>
+      <c r="A257" s="22" t="s">
+        <v>155</v>
       </c>
       <c r="B257" s="1">
         <v>256</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D257" s="4">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="D257" s="1">
+        <v>1</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F257" s="2"/>
       <c r="G257" s="1">
-        <v>193</v>
-      </c>
-      <c r="H257" s="8"/>
-      <c r="I257" s="1"/>
+        <v>88</v>
+      </c>
+      <c r="H257" s="2"/>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B258" s="1">
         <v>257</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D258" s="4">
         <v>0</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>77</v>
+        <v>14</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="G258" s="1">
-        <v>204</v>
-      </c>
-      <c r="H258" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="H258" s="1"/>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B259" s="1">
         <v>258</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="D259" s="4">
         <v>0</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F259" s="1"/>
       <c r="G259" s="1">
-        <v>204</v>
+        <v>11</v>
       </c>
       <c r="H259" s="8"/>
-    </row>
-    <row r="260" spans="1:9">
+      <c r="I259" s="1"/>
+    </row>
+    <row r="260" spans="1:9" ht="15.75">
       <c r="A260" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B260" s="1">
         <v>259</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D260" s="4">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="D260" s="1">
+        <v>1</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F260" s="1"/>
       <c r="G260" s="1">
-        <v>204</v>
+        <v>10</v>
       </c>
       <c r="H260" s="8"/>
+      <c r="I260" s="1"/>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B261" s="1">
         <v>260</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D261" s="4">
         <v>0</v>
@@ -8036,55 +8149,56 @@
         <v>9</v>
       </c>
       <c r="G261" s="1">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="H261" s="8"/>
+      <c r="I261" s="1"/>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B262" s="1">
         <v>261</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="D262" s="4">
         <v>0</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="G262" s="1">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="H262" s="8"/>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B263" s="1">
         <v>262</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D263" s="1">
-        <v>1</v>
+        <v>148</v>
+      </c>
+      <c r="D263" s="4">
+        <v>0</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="G263" s="1">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="H263" s="8"/>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B264" s="1">
         <v>263</v>
@@ -8092,26 +8206,26 @@
       <c r="C264" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D264" s="1">
-        <v>1</v>
+      <c r="D264" s="4">
+        <v>0</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G264" s="1">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="H264" s="8"/>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B265" s="1">
         <v>264</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D265" s="4">
         <v>0</v>
@@ -8120,229 +8234,228 @@
         <v>9</v>
       </c>
       <c r="G265" s="1">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="H265" s="8"/>
     </row>
     <row r="266" spans="1:9">
-      <c r="A266" s="24" t="s">
-        <v>162</v>
+      <c r="A266" s="23" t="s">
+        <v>156</v>
       </c>
       <c r="B266" s="1">
         <v>265</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D266" s="1">
-        <v>1</v>
+        <v>158</v>
+      </c>
+      <c r="D266" s="4">
+        <v>0</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F266" s="1"/>
-      <c r="G266" s="1" t="s">
-        <v>164</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G266" s="1">
+        <v>218</v>
+      </c>
+      <c r="H266" s="8"/>
     </row>
     <row r="267" spans="1:9">
-      <c r="A267" s="24" t="s">
-        <v>162</v>
+      <c r="A267" s="23" t="s">
+        <v>156</v>
       </c>
       <c r="B267" s="1">
         <v>266</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D267" s="4">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="D267" s="1">
+        <v>1</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="G267" s="1">
-        <v>208</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="H267" s="8"/>
     </row>
     <row r="268" spans="1:9">
-      <c r="A268" s="25" t="s">
-        <v>165</v>
+      <c r="A268" s="23" t="s">
+        <v>156</v>
       </c>
       <c r="B268" s="1">
         <v>267</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>166</v>
+        <v>31</v>
       </c>
       <c r="D268" s="1">
         <v>1</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F268" s="1"/>
+        <v>9</v>
+      </c>
       <c r="G268" s="1">
-        <v>24</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="H268" s="8"/>
     </row>
     <row r="269" spans="1:9">
-      <c r="A269" s="25" t="s">
-        <v>165</v>
+      <c r="A269" s="23" t="s">
+        <v>156</v>
       </c>
       <c r="B269" s="1">
         <v>268</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D269" s="1">
-        <v>1</v>
+        <v>159</v>
+      </c>
+      <c r="D269" s="4">
+        <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F269" s="1"/>
       <c r="G269" s="1">
-        <v>45</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="H269" s="8"/>
     </row>
     <row r="270" spans="1:9">
-      <c r="A270" s="25" t="s">
-        <v>165</v>
+      <c r="A270" s="24" t="s">
+        <v>160</v>
       </c>
       <c r="B270" s="1">
         <v>269</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D270" s="1">
         <v>1</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="F270" s="1"/>
-      <c r="G270" s="1">
-        <v>48</v>
+      <c r="G270" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="271" spans="1:9">
-      <c r="A271" s="25" t="s">
-        <v>165</v>
+      <c r="A271" s="24" t="s">
+        <v>160</v>
       </c>
       <c r="B271" s="1">
         <v>270</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D271" s="1">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="D271" s="4">
+        <v>0</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F271" s="1"/>
+        <v>100</v>
+      </c>
       <c r="G271" s="1">
-        <v>48</v>
+        <v>208</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B272" s="1">
         <v>271</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D272" s="1">
         <v>1</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F272" s="1"/>
       <c r="G272" s="1">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="273" spans="1:8">
       <c r="A273" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B273" s="1">
         <v>272</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="D273" s="1">
         <v>1</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F273" s="1"/>
       <c r="G273" s="1">
-        <v>179</v>
+        <v>45</v>
       </c>
     </row>
     <row r="274" spans="1:8">
       <c r="A274" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B274" s="1">
         <v>273</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D274" s="4">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="D274" s="1">
+        <v>1</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>77</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F274" s="1"/>
       <c r="G274" s="1">
-        <v>159</v>
-      </c>
-      <c r="H274" s="3" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B275" s="1">
         <v>274</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="D275" s="1">
         <v>1</v>
       </c>
-      <c r="E275" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="E275" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F275" s="1"/>
       <c r="G275" s="1">
-        <v>201</v>
+        <v>48</v>
       </c>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B276" s="1">
         <v>275</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D276" s="1">
         <v>1</v>
@@ -8350,235 +8463,230 @@
       <c r="E276" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F276" s="1"/>
       <c r="G276" s="1">
-        <v>201</v>
+        <v>59</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B277" s="1">
         <v>276</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D277" s="4">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="D277" s="1">
+        <v>1</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F277" s="1"/>
       <c r="G277" s="1">
-        <v>220</v>
+        <v>179</v>
       </c>
     </row>
     <row r="278" spans="1:8">
-      <c r="A278" s="26" t="s">
-        <v>169</v>
+      <c r="A278" s="25" t="s">
+        <v>163</v>
       </c>
       <c r="B278" s="1">
         <v>277</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D278" s="4">
         <v>0</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="G278" s="1">
-        <v>7</v>
-      </c>
-      <c r="H278" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="H278" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="279" spans="1:8">
-      <c r="A279" s="26" t="s">
-        <v>169</v>
+      <c r="A279" s="25" t="s">
+        <v>163</v>
       </c>
       <c r="B279" s="1">
         <v>278</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D279" s="1">
         <v>1</v>
       </c>
-      <c r="E279" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F279" s="2"/>
+      <c r="E279" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="G279" s="1">
-        <v>41</v>
-      </c>
-      <c r="H279" s="2"/>
+        <v>201</v>
+      </c>
     </row>
     <row r="280" spans="1:8">
-      <c r="A280" s="26" t="s">
-        <v>169</v>
+      <c r="A280" s="25" t="s">
+        <v>163</v>
       </c>
       <c r="B280" s="1">
         <v>279</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="D280" s="1">
         <v>1</v>
       </c>
       <c r="E280" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G280" s="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" s="25" t="s">
         <v>163</v>
-      </c>
-      <c r="F280" s="2"/>
-      <c r="G280" s="1">
-        <v>89</v>
-      </c>
-      <c r="H280" s="2"/>
-    </row>
-    <row r="281" spans="1:8">
-      <c r="A281" s="26" t="s">
-        <v>169</v>
       </c>
       <c r="B281" s="1">
         <v>280</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D281" s="1">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="D281" s="4">
+        <v>0</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F281" s="2"/>
+        <v>9</v>
+      </c>
       <c r="G281" s="1">
-        <v>100</v>
-      </c>
-      <c r="H281" s="2"/>
+        <v>220</v>
+      </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B282" s="1">
         <v>281</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D282" s="1">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="D282" s="4">
+        <v>0</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F282" s="2"/>
+      <c r="F282" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="G282" s="1">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="H282" s="2"/>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B283" s="1">
         <v>282</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D283" s="4">
-        <v>0</v>
+        <v>169</v>
+      </c>
+      <c r="D283" s="1">
+        <v>1</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>170</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="F283" s="2"/>
       <c r="G283" s="1">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="H283" s="2"/>
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B284" s="1">
         <v>283</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D284" s="1">
         <v>1</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="1">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="H284" s="2"/>
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B285" s="1">
         <v>284</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="D285" s="1">
         <v>1</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="1">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H285" s="2"/>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B286" s="1">
         <v>285</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D286" s="1">
         <v>1</v>
       </c>
-      <c r="E286" s="2" t="s">
-        <v>49</v>
+      <c r="E286" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="1">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="H286" s="2"/>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B287" s="1">
         <v>286</v>
@@ -8586,206 +8694,204 @@
       <c r="C287" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D287" s="1">
-        <v>1</v>
+      <c r="D287" s="4">
+        <v>0</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>126</v>
+        <v>100</v>
+      </c>
+      <c r="F287" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="G287" s="1">
-        <v>210</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="H287" s="2"/>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B288" s="1">
         <v>287</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D288" s="4">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="D288" s="1">
+        <v>1</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F288" s="2"/>
       <c r="G288" s="1">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9">
-      <c r="A289" s="2" t="s">
-        <v>174</v>
+        <v>147</v>
+      </c>
+      <c r="H288" s="2"/>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="B289" s="1">
         <v>288</v>
       </c>
-      <c r="C289" s="2" t="s">
-        <v>17</v>
+      <c r="C289" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D289" s="1">
         <v>1</v>
       </c>
-      <c r="E289" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="E289" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F289" s="2"/>
       <c r="G289" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9">
-      <c r="A290" s="2" t="s">
-        <v>175</v>
+        <v>148</v>
+      </c>
+      <c r="H289" s="2"/>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="B290" s="1">
         <v>289</v>
       </c>
-      <c r="C290" s="2" t="s">
-        <v>31</v>
+      <c r="C290" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D290" s="1">
         <v>1</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F290" s="2"/>
       <c r="G290" s="1">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9">
-      <c r="A291" s="2" t="s">
-        <v>175</v>
+        <v>122</v>
+      </c>
+      <c r="H290" s="2"/>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="B291" s="1">
         <v>290</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>31</v>
+      <c r="C291" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D291" s="1">
         <v>1</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>175</v>
+      <c r="E291" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="G291" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9">
-      <c r="A292" s="1" t="s">
-        <v>176</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="B292" s="1">
         <v>291</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="D292" s="4">
         <v>0</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="G292" s="1">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9">
-      <c r="A293" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="B293" s="1">
         <v>292</v>
       </c>
-      <c r="C293" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D293" s="4">
-        <v>0</v>
-      </c>
-      <c r="E293" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F293" s="1" t="s">
-        <v>177</v>
+      <c r="C293" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D293" s="1">
+        <v>1</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="G293" s="1">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9">
-      <c r="A294" s="1" t="s">
-        <v>178</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B294" s="1">
         <v>293</v>
       </c>
-      <c r="C294" s="1" t="s">
+      <c r="C294" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D294" s="4">
-        <v>0</v>
-      </c>
-      <c r="E294" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F294" s="1" t="s">
-        <v>178</v>
+      <c r="D294" s="1">
+        <v>1</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F294" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="G294" s="1">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9">
-      <c r="A295" s="1" t="s">
-        <v>176</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B295" s="1">
         <v>294</v>
       </c>
-      <c r="C295" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D295" s="4">
-        <v>0</v>
-      </c>
-      <c r="E295" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F295" s="1" t="s">
-        <v>176</v>
+      <c r="C295" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D295" s="1">
+        <v>1</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F295" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="G295" s="1">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
       <c r="A296" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B296" s="1">
         <v>295</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D296" s="4">
         <v>0</v>
@@ -8794,15 +8900,15 @@
         <v>77</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G296" s="1">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
       <c r="A297" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B297" s="1">
         <v>296</v>
@@ -8810,21 +8916,21 @@
       <c r="C297" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D297" s="1">
-        <v>1</v>
+      <c r="D297" s="4">
+        <v>0</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G297" s="1">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9">
-      <c r="A298" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B298" s="1">
@@ -8833,192 +8939,185 @@
       <c r="C298" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D298" s="1">
-        <v>1</v>
+      <c r="D298" s="4">
+        <v>0</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F298" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F298" s="1" t="s">
         <v>175</v>
       </c>
       <c r="G298" s="1">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
       <c r="A299" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B299" s="1">
         <v>298</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D299" s="1">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D299" s="4">
+        <v>0</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G299" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
       <c r="A300" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B300" s="1">
         <v>299</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D300" s="4">
         <v>0</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G300" s="1">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
       <c r="A301" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B301" s="1">
         <v>300</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D301" s="1">
         <v>1</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="G301" s="1">
-        <v>57</v>
-      </c>
-      <c r="H301" s="1"/>
-      <c r="I301" s="1"/>
-    </row>
-    <row r="302" spans="1:9">
-      <c r="A302" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B302" s="1">
         <v>301</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D302" s="1">
         <v>1</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F302" s="1" t="s">
-        <v>181</v>
+        <v>9</v>
+      </c>
+      <c r="F302" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="G302" s="1">
-        <v>57</v>
-      </c>
-      <c r="H302" s="2"/>
-      <c r="I302" s="1"/>
-    </row>
-    <row r="303" spans="1:9">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
       <c r="A303" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B303" s="1">
         <v>302</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="D303" s="1">
         <v>1</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>183</v>
+        <v>9</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G303" s="1">
-        <v>105</v>
-      </c>
-      <c r="H303" s="2"/>
-      <c r="I303" s="1"/>
-    </row>
-    <row r="304" spans="1:9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
       <c r="A304" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B304" s="1">
         <v>303</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D304" s="1">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D304" s="4">
+        <v>0</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G304" s="1">
-        <v>178</v>
-      </c>
-      <c r="H304" s="2"/>
-      <c r="I304" s="1"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B305" s="1">
         <v>304</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D305" s="4">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="D305" s="1">
+        <v>1</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G305" s="1">
-        <v>163</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H305" s="1"/>
       <c r="I305" s="1"/>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B306" s="1">
         <v>305</v>
@@ -9026,23 +9125,24 @@
       <c r="C306" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D306" s="4">
-        <v>0</v>
+      <c r="D306" s="1">
+        <v>1</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G306" s="1">
-        <v>167</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H306" s="2"/>
       <c r="I306" s="1"/>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B307" s="1">
         <v>306</v>
@@ -9054,90 +9154,93 @@
         <v>1</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G307" s="1">
-        <v>188</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="H307" s="2"/>
       <c r="I307" s="1"/>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B308" s="1">
         <v>307</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D308" s="4">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="D308" s="1">
+        <v>1</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="G308" s="1">
-        <v>106</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="H308" s="2"/>
       <c r="I308" s="1"/>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B309" s="1">
         <v>308</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D309" s="1">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="D309" s="4">
+        <v>0</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G309" s="1">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="I309" s="1"/>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B310" s="1">
         <v>309</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D310" s="1">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D310" s="4">
+        <v>0</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G310" s="1">
-        <v>202</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I310" s="1"/>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B311" s="1">
         <v>310</v>
@@ -9145,241 +9248,244 @@
       <c r="C311" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D311" s="4">
-        <v>0</v>
+      <c r="D311" s="1">
+        <v>1</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G311" s="1">
-        <v>205</v>
-      </c>
-      <c r="H311" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="I311" s="1"/>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B312" s="1">
         <v>311</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D312" s="1">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="D312" s="4">
+        <v>0</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G312" s="1">
-        <v>205</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="I312" s="1"/>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B313" s="1">
         <v>312</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D313" s="1">
         <v>1</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G313" s="1">
-        <v>205</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="I313" s="1"/>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B314" s="1">
         <v>313</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D314" s="4">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="D314" s="1">
+        <v>1</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G314" s="1">
-        <v>223</v>
-      </c>
-      <c r="H314" s="3" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B315" s="1">
         <v>314</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D315" s="1">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="D315" s="4">
+        <v>0</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G315" s="1">
-        <v>223</v>
+        <v>205</v>
+      </c>
+      <c r="H315" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B316" s="1">
         <v>315</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D316" s="4">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="D316" s="1">
+        <v>1</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G316" s="1">
-        <v>229</v>
+        <v>205</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B317" s="1">
         <v>316</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D317" s="1">
         <v>1</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G317" s="1">
-        <v>19</v>
+        <v>205</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B318" s="1">
         <v>317</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D318" s="1">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="D318" s="4">
+        <v>0</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="G318" s="1">
-        <v>47</v>
+        <v>223</v>
+      </c>
+      <c r="H318" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" s="1" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B319" s="1">
         <v>318</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D319" s="1">
         <v>1</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="G319" s="1">
-        <v>71</v>
+        <v>223</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B320" s="1">
         <v>319</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D320" s="1">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="D320" s="4">
+        <v>0</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G320" s="1">
-        <v>71</v>
+        <v>229</v>
       </c>
     </row>
     <row r="321" spans="1:8">
       <c r="A321" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B321" s="1">
         <v>320</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D321" s="1">
         <v>1</v>
@@ -9388,61 +9494,61 @@
         <v>9</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G321" s="1">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8" ht="15" customHeight="1">
-      <c r="A322" s="27" t="s">
-        <v>194</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="B322" s="1">
         <v>321</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="D322" s="1">
         <v>1</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F322" s="27" t="s">
-        <v>196</v>
+        <v>14</v>
+      </c>
+      <c r="F322" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="G322" s="1">
-        <v>140</v>
+        <v>47</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B323" s="1">
         <v>322</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D323" s="1">
         <v>1</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G323" s="1">
-        <v>154</v>
+        <v>71</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B324" s="1">
         <v>323</v>
@@ -9457,156 +9563,153 @@
         <v>9</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G324" s="1">
-        <v>154</v>
+        <v>71</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="1" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="B325" s="1">
         <v>324</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D325" s="1">
         <v>1</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="G325" s="1">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8">
-      <c r="A326" s="1" t="s">
-        <v>197</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" ht="15" customHeight="1">
+      <c r="A326" s="27" t="s">
+        <v>191</v>
       </c>
       <c r="B326" s="1">
         <v>325</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="D326" s="1">
         <v>1</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F326" s="1" t="s">
-        <v>197</v>
+        <v>9</v>
+      </c>
+      <c r="F326" s="27" t="s">
+        <v>193</v>
       </c>
       <c r="G326" s="1">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B327" s="1">
         <v>326</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D327" s="4">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="D327" s="1">
+        <v>1</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="G327" s="1">
-        <v>180</v>
+        <v>154</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B328" s="1">
         <v>327</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D328" s="1">
         <v>1</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="G328" s="1">
-        <v>180</v>
+        <v>154</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B329" s="1">
         <v>328</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D329" s="4">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="D329" s="1">
+        <v>1</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G329" s="1">
-        <v>158</v>
-      </c>
-      <c r="H329" s="3" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B330" s="1">
         <v>329</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D330" s="4">
-        <v>0</v>
+        <v>123</v>
+      </c>
+      <c r="D330" s="1">
+        <v>1</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G330" s="1">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B331" s="1">
         <v>330</v>
@@ -9621,18 +9724,15 @@
         <v>77</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G331" s="1">
-        <v>160</v>
-      </c>
-      <c r="H331" s="3" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B332" s="1">
         <v>331</v>
@@ -9644,42 +9744,44 @@
         <v>1</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G332" s="1">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="333" spans="1:8">
       <c r="A333" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B333" s="1">
         <v>332</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D333" s="4">
         <v>0</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G333" s="1">
-        <v>67</v>
-      </c>
-      <c r="H333" s="21"/>
+        <v>158</v>
+      </c>
+      <c r="H333" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="334" spans="1:8">
       <c r="A334" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B334" s="1">
         <v>333</v>
@@ -9687,23 +9789,22 @@
       <c r="C334" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D334" s="1">
-        <v>1</v>
+      <c r="D334" s="4">
+        <v>0</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="G334" s="1">
-        <v>181</v>
-      </c>
-      <c r="H334" s="1"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B335" s="1">
         <v>334</v>
@@ -9715,49 +9816,50 @@
         <v>0</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="G335" s="1">
-        <v>181</v>
-      </c>
-      <c r="H335" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="H335" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="336" spans="1:8">
       <c r="A336" s="1" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B336" s="1">
         <v>335</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D336" s="1">
         <v>1</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="G336" s="1">
-        <v>169</v>
-      </c>
-      <c r="H336" s="1"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B337" s="1">
         <v>336</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="D337" s="4">
         <v>0</v>
@@ -9766,61 +9868,64 @@
         <v>9</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G337" s="1">
-        <v>137</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H337" s="21"/>
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B338" s="1">
         <v>337</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D338" s="1">
         <v>1</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G338" s="1">
-        <v>208</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="H338" s="1"/>
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B339" s="1">
         <v>338</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D339" s="1">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="D339" s="4">
+        <v>0</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G339" s="1">
-        <v>208</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="H339" s="1"/>
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B340" s="1">
         <v>339</v>
@@ -9835,182 +9940,179 @@
         <v>9</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G340" s="1">
-        <v>238</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="H340" s="1"/>
     </row>
     <row r="341" spans="1:9">
-      <c r="A341" s="2" t="s">
-        <v>204</v>
+      <c r="A341" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="B341" s="1">
         <v>340</v>
       </c>
-      <c r="C341" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D341" s="1">
-        <v>1</v>
+      <c r="C341" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D341" s="4">
+        <v>0</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F341" s="2" t="s">
-        <v>204</v>
+      <c r="F341" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="G341" s="1">
-        <v>227</v>
+        <v>137</v>
       </c>
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B342" s="1">
         <v>341</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D342" s="1">
         <v>1</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G342" s="1">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9" ht="30">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9">
       <c r="A343" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B343" s="1">
         <v>342</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D343" s="4">
-        <v>0</v>
-      </c>
-      <c r="E343" s="27" t="s">
-        <v>206</v>
+        <v>31</v>
+      </c>
+      <c r="D343" s="1">
+        <v>1</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G343" s="1">
-        <v>129</v>
-      </c>
-      <c r="H343" s="1"/>
-      <c r="I343" s="1"/>
+        <v>208</v>
+      </c>
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B344" s="1">
         <v>343</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D344" s="1">
         <v>1</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="G344" s="1">
-        <v>182</v>
-      </c>
-      <c r="H344" s="1"/>
-      <c r="I344" s="1"/>
+        <v>238</v>
+      </c>
     </row>
     <row r="345" spans="1:9">
-      <c r="A345" s="1" t="s">
-        <v>208</v>
+      <c r="A345" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="B345" s="1">
         <v>344</v>
       </c>
-      <c r="C345" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D345" s="4">
-        <v>0</v>
+      <c r="C345" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D345" s="1">
+        <v>1</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F345" s="1" t="s">
-        <v>208</v>
+        <v>9</v>
+      </c>
+      <c r="F345" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="G345" s="1">
-        <v>171</v>
-      </c>
-      <c r="H345" s="8"/>
+        <v>227</v>
+      </c>
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B346" s="1">
         <v>345</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D346" s="4">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="D346" s="1">
+        <v>1</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G346" s="1">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="347" spans="1:9">
-      <c r="A347" s="2" t="s">
-        <v>202</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" ht="30">
+      <c r="A347" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="B347" s="1">
         <v>346</v>
       </c>
-      <c r="C347" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D347" s="1">
-        <v>1</v>
-      </c>
-      <c r="E347" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F347" s="2" t="s">
-        <v>202</v>
+      <c r="C347" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D347" s="4">
+        <v>0</v>
+      </c>
+      <c r="E347" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="F347" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="G347" s="1">
-        <v>190</v>
-      </c>
-      <c r="H347" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="H347" s="1"/>
+      <c r="I347" s="1"/>
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B348" s="1">
         <v>347</v>
@@ -10018,29 +10120,30 @@
       <c r="C348" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D348" s="4">
-        <v>0</v>
+      <c r="D348" s="1">
+        <v>1</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G348" s="1">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H348" s="1"/>
+      <c r="I348" s="1"/>
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B349" s="1">
         <v>348</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="D349" s="4">
         <v>0</v>
@@ -10049,56 +10152,151 @@
         <v>28</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G349" s="1">
-        <v>126</v>
-      </c>
-      <c r="H349" s="1"/>
+        <v>171</v>
+      </c>
+      <c r="H349" s="8"/>
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B350" s="1">
         <v>349</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D350" s="1">
-        <v>1</v>
+        <v>206</v>
+      </c>
+      <c r="D350" s="4">
+        <v>0</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G350" s="1">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B351" s="1">
+        <v>350</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D351" s="1">
+        <v>1</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F351" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G351" s="1">
+        <v>190</v>
+      </c>
+      <c r="H351" s="2"/>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B352" s="1">
+        <v>351</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D352" s="4">
+        <v>0</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G352" s="1">
+        <v>173</v>
+      </c>
+      <c r="H352" s="1"/>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B353" s="1">
+        <v>352</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D353" s="4">
+        <v>0</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G353" s="1">
         <v>126</v>
       </c>
-      <c r="H350" s="1"/>
-    </row>
-    <row r="351" spans="1:9">
-      <c r="A351" s="1"/>
-      <c r="B351" s="1"/>
-      <c r="C351" s="1"/>
-      <c r="D351" s="28"/>
-      <c r="E351" s="1"/>
-      <c r="F351" s="1"/>
-      <c r="G351" s="1"/>
-      <c r="H351" s="1"/>
-    </row>
-    <row r="352" spans="1:9">
-      <c r="A352" s="1"/>
-      <c r="B352" s="1"/>
-      <c r="C352" s="1"/>
-      <c r="D352" s="28"/>
-      <c r="E352" s="1"/>
-      <c r="F352" s="1"/>
-      <c r="G352" s="1"/>
-      <c r="H352" s="1"/>
+      <c r="H353" s="1"/>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B354" s="1">
+        <v>353</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D354" s="1">
+        <v>1</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G354" s="1">
+        <v>126</v>
+      </c>
+      <c r="H354" s="1"/>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="1"/>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="28"/>
+      <c r="E355" s="1"/>
+      <c r="F355" s="1"/>
+      <c r="G355" s="1"/>
+      <c r="H355" s="1"/>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" s="1"/>
+      <c r="B356" s="1"/>
+      <c r="C356" s="1"/>
+      <c r="D356" s="28"/>
+      <c r="E356" s="1"/>
+      <c r="F356" s="1"/>
+      <c r="G356" s="1"/>
+      <c r="H356" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
